--- a/bilans_uspjeha.xlsx
+++ b/bilans_uspjeha.xlsx
@@ -365,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -382,6 +382,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -392,14 +393,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -715,28 +709,29 @@
     <col min="2" max="2" width="17.140625" style="3" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="7.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9">
+      <c r="B1" s="10">
         <v>2023</v>
       </c>
-      <c r="C1" s="8">
+      <c r="C1" s="9">
         <v>2022</v>
       </c>
-      <c r="D1" s="8">
+      <c r="D1" s="9">
         <v>2021</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -895,6 +890,7 @@
       <c r="D14" s="7">
         <v>2264972</v>
       </c>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -924,7 +920,7 @@
         <v>2668750</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>11</v>
       </c>
@@ -938,7 +934,7 @@
         <v>2297719</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
@@ -952,7 +948,7 @@
         <v>371031</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -966,7 +962,7 @@
         <v>857833</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>30</v>
       </c>
@@ -980,7 +976,7 @@
         <v>611005</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>31</v>
       </c>
@@ -993,8 +989,9 @@
       <c r="D21" s="7">
         <v>611005</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1008,7 +1005,7 @@
         <v>611005</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>4</v>
       </c>
@@ -1020,7 +1017,7 @@
       </c>
       <c r="D23" s="7"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
@@ -1030,9 +1027,12 @@
       <c r="C24" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D24" s="7"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D24" s="7">
+        <f>D14+D16+D15+D19+D20+D27+D28</f>
+        <v>7049621</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>6</v>
       </c>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D25" s="7"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D26" s="7"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>425426</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>11363</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D29" s="7"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>334988</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D31" s="7"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -1895,7 +1895,7 @@
     <mergeCell ref="C1:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:D92">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(), 2)=1</formula>
     </cfRule>
   </conditionalFormatting>
